--- a/data/trans_orig/cron_index-Clase-trans_orig.xlsx
+++ b/data/trans_orig/cron_index-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de cronicidad total</t>
+          <t>Índice de cronicidad total (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,54</t>
+          <t>0,37; 0,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -731,42 +731,42 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 0,99</t>
+          <t>0,77; 0,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,53</t>
+          <t>0,33; 0,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,54</t>
+          <t>0,32; 0,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 0,61</t>
+          <t>0,4; 0,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 0,84</t>
+          <t>0,65; 0,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,5</t>
+          <t>0,37; 0,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 0,53</t>
+          <t>0,39; 0,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,6</t>
+          <t>0,46; 0,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,57</t>
+          <t>0,39; 0,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,67</t>
+          <t>0,47; 0,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -876,42 +876,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,5</t>
+          <t>0,3; 0,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,56</t>
+          <t>0,35; 0,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,52</t>
+          <t>0,34; 0,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,77</t>
+          <t>0,6; 0,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,49</t>
+          <t>0,36; 0,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,53</t>
+          <t>0,4; 0,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,57</t>
+          <t>0,43; 0,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 0,87</t>
+          <t>0,72; 0,87</t>
         </is>
       </c>
     </row>
@@ -996,42 +996,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,62</t>
+          <t>0,45; 0,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,94</t>
+          <t>0,73; 0,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,77</t>
+          <t>0,6; 0,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,14</t>
+          <t>0,27; 1,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,84</t>
+          <t>0,51; 0,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,92</t>
+          <t>0,63; 0,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,1</t>
+          <t>0,68; 1,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,4</t>
+          <t>1,03; 1,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,91</t>
+          <t>0,72; 0,89</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,16</t>
+          <t>0,35; 1,15</t>
         </is>
       </c>
     </row>
@@ -1151,37 +1151,37 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,1</t>
+          <t>0,91; 1,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,67</t>
+          <t>0,52; 0,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,6</t>
+          <t>0,46; 0,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,58</t>
+          <t>0,44; 0,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,11</t>
+          <t>0,77; 1,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,67</t>
+          <t>0,57; 0,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,69</t>
+          <t>0,58; 0,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,66</t>
+          <t>0,89; 1,71</t>
         </is>
       </c>
     </row>
@@ -1276,32 +1276,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,65</t>
+          <t>0,42; 0,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,74</t>
+          <t>0,53; 0,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,83</t>
+          <t>0,64; 0,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,18</t>
+          <t>0,91; 1,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,82</t>
+          <t>0,63; 0,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,05</t>
+          <t>0,86; 1,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,27 +1311,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,5</t>
+          <t>1,18; 1,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,72</t>
+          <t>0,58; 0,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 0,89</t>
+          <t>0,75; 0,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 0,87</t>
+          <t>0,74; 0,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 1,36</t>
+          <t>1,12; 1,36</t>
         </is>
       </c>
     </row>
@@ -1421,17 +1421,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,3</t>
+          <t>0,14; 0,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,28</t>
+          <t>0,14; 0,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,57</t>
+          <t>0,21; 0,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,25</t>
+          <t>1,08; 1,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,37</t>
+          <t>1,15; 1,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,13</t>
+          <t>0,95; 1,14</t>
         </is>
       </c>
     </row>
@@ -1556,22 +1556,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,54</t>
+          <t>0,47; 0,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>0,59; 0,67</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>0,58; 0,66</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0,58; 0,66</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,95</t>
+          <t>0,68; 0,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1586,12 +1586,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 0,8</t>
+          <t>0,72; 0,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,52</t>
+          <t>1,01; 1,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">

--- a/data/trans_orig/cron_index-Clase-trans_orig.xlsx
+++ b/data/trans_orig/cron_index-Clase-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,82</t>
         </is>
       </c>
     </row>
@@ -721,42 +721,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,59</t>
+          <t>0,41; 0,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,66</t>
+          <t>0,46; 0,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 0,99</t>
+          <t>0,79; 1,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,52</t>
+          <t>0,33; 0,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,56</t>
+          <t>0,32; 0,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 0,62</t>
+          <t>0,39; 0,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 0,82</t>
+          <t>0,65; 0,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,49</t>
+          <t>0,38; 0,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 0,88</t>
+          <t>0,76; 0,9</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,55</t>
+          <t>0,36; 0,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,02</t>
+          <t>0,78; 0,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,49</t>
+          <t>0,3; 0,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,27 +886,27 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,52</t>
+          <t>0,33; 0,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,78</t>
+          <t>0,61; 0,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,49</t>
+          <t>0,35; 0,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 0,53</t>
+          <t>0,39; 0,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,57</t>
+          <t>0,42; 0,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>1,09</t>
         </is>
       </c>
     </row>
@@ -996,42 +996,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,61</t>
+          <t>0,45; 0,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 0,95</t>
+          <t>0,72; 0,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,77</t>
+          <t>0,59; 0,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,14</t>
+          <t>0,92; 1,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,86</t>
+          <t>0,5; 0,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,91</t>
+          <t>0,64; 0,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,09</t>
+          <t>0,69; 1,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,42</t>
+          <t>1,01; 1,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,17 +1041,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,89</t>
+          <t>0,72; 0,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 0,81</t>
+          <t>0,65; 0,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,15</t>
+          <t>0,98; 1,22</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,26</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>0,91</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,7</t>
+          <t>0,57; 0,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 0,79</t>
+          <t>0,64; 0,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 0,69</t>
+          <t>0,51; 0,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,61</t>
+          <t>0,46; 0,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1171,17 +1171,17 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,95</t>
+          <t>0,73; 0,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,66</t>
+          <t>0,57; 0,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,69</t>
+          <t>0,59; 0,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,71</t>
+          <t>0,85; 0,96</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,24</t>
+          <t>1,16</t>
         </is>
       </c>
     </row>
@@ -1276,42 +1276,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,63</t>
+          <t>0,42; 0,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,74</t>
+          <t>0,53; 0,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 0,84</t>
+          <t>0,64; 0,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,18</t>
+          <t>0,83; 1,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,81</t>
+          <t>0,63; 0,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,06</t>
+          <t>0,85; 1,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 0,97</t>
+          <t>0,78; 0,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,5</t>
+          <t>1,21; 1,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1331,14 +1331,14 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,36</t>
+          <t>1,08; 1,24</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,26</t>
+          <t>1,23</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>1,03</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,16</t>
+          <t>0,08; 0,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,58</t>
+          <t>0,19; 0,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1441,17 +1441,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,26</t>
+          <t>1,07; 1,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,15</t>
+          <t>0,97; 1,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,36</t>
+          <t>1,13; 1,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,14</t>
+          <t>0,94; 1,12</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>0,96</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,54</t>
+          <t>0,48; 0,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,66</t>
+          <t>0,58; 0,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 0,94</t>
+          <t>0,86; 0,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,51</t>
+          <t>0,97; 1,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,2</t>
+          <t>0,93; 1,0</t>
         </is>
       </c>
     </row>
